--- a/Trabalho M2/OUTPUT_3.3.c_MELHORES_RN/Common/Resumo_Melhores_RN_Guardadas.xlsx
+++ b/Trabalho M2/OUTPUT_3.3.c_MELHORES_RN/Common/Resumo_Melhores_RN_Guardadas.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="172" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="215" uniqueCount="38">
   <si>
     <t>rank_guardado</t>
   </si>
@@ -115,6 +115,18 @@
   </si>
   <si>
     <t>[5 5]</t>
+  </si>
+  <si>
+    <t>RN_MICE_NORM_Topo-14_trainlm_logsig_MF6_Div-0.6-0.2-0.2</t>
+  </si>
+  <si>
+    <t>RN_MICE_NORM_Topo-10_trainscg_softmax_MF6_Div-0.6-0.2-0.2</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>[0.6 0.2 0.2]</t>
   </si>
 </sst>
 </file>
@@ -164,7 +176,7 @@
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.6328125" customWidth="true"/>
-    <col min="2" max="2" width="58.1796875" customWidth="true"/>
+    <col min="2" max="2" width="58" customWidth="true"/>
     <col min="3" max="3" width="47" customWidth="true"/>
     <col min="4" max="4" width="8.7265625" customWidth="true"/>
     <col min="5" max="5" width="9.26953125" customWidth="true"/>
@@ -236,7 +248,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>2</v>
+        <v>34</v>
       </c>
       <c r="C2" s="0" t="s">
         <v>6</v>
@@ -248,7 +260,7 @@
         <v>12</v>
       </c>
       <c r="F2" s="0" t="s">
-        <v>14</v>
+        <v>36</v>
       </c>
       <c r="G2" s="0" t="s">
         <v>16</v>
@@ -260,25 +272,25 @@
         <v>21</v>
       </c>
       <c r="J2" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K2" s="0">
         <v>6</v>
       </c>
       <c r="L2" s="0">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M2" s="0">
         <v>100</v>
       </c>
       <c r="N2" s="0">
-        <v>16.68150076513934</v>
+        <v>16.672852876129525</v>
       </c>
       <c r="O2" s="0">
-        <v>99.980000000000004</v>
+        <v>100</v>
       </c>
       <c r="P2" s="0">
-        <v>16.675107495532426</v>
+        <v>16.667934026392725</v>
       </c>
     </row>
     <row r="3">
@@ -286,7 +298,7 @@
         <v>2</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>31</v>
+        <v>3</v>
       </c>
       <c r="C3" s="0" t="s">
         <v>7</v>
@@ -298,10 +310,10 @@
         <v>12</v>
       </c>
       <c r="F3" s="0" t="s">
-        <v>33</v>
+        <v>14</v>
       </c>
       <c r="G3" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H3" s="0" t="s">
         <v>19</v>
@@ -322,13 +334,13 @@
         <v>100</v>
       </c>
       <c r="N3" s="0">
-        <v>16.669052542998688</v>
+        <v>16.668733121774466</v>
       </c>
       <c r="O3" s="0">
-        <v>99.980000000000004</v>
+        <v>99.939999999999998</v>
       </c>
       <c r="P3" s="0">
-        <v>16.675815510859664</v>
+        <v>16.690337214435171</v>
       </c>
     </row>
     <row r="4">
@@ -336,7 +348,7 @@
         <v>3</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C4" s="0" t="s">
         <v>8</v>
@@ -351,7 +363,7 @@
         <v>14</v>
       </c>
       <c r="G4" s="0" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H4" s="0" t="s">
         <v>19</v>
@@ -360,7 +372,7 @@
         <v>22</v>
       </c>
       <c r="J4" s="0" t="s">
-        <v>24</v>
+        <v>37</v>
       </c>
       <c r="K4" s="0">
         <v>6</v>
@@ -372,13 +384,13 @@
         <v>100</v>
       </c>
       <c r="N4" s="0">
-        <v>16.670153675236442</v>
+        <v>16.667371485398604</v>
       </c>
       <c r="O4" s="0">
-        <v>99.980000000000004</v>
+        <v>100</v>
       </c>
       <c r="P4" s="0">
-        <v>16.674575077980208</v>
+        <v>16.667196862818376</v>
       </c>
     </row>
   </sheetData>
